--- a/AAII_Financials/Quarterly/BELF.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BELF.A_QTR_FIN.xlsx
@@ -653,149 +653,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>149900</v>
+      </c>
+      <c r="E8" s="3">
         <v>123600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>133200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>128100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>140000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>158700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>168800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>172300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>169200</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>93700</v>
+      </c>
+      <c r="E9" s="3">
         <v>79000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>79800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>80000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>88800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>103200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>113200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>118700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>116700</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E10" s="3">
         <v>44700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>53400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>48100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>51200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>55500</v>
       </c>
       <c r="I10" s="3">
         <v>55500</v>
       </c>
       <c r="J10" s="3">
+        <v>55500</v>
+      </c>
+      <c r="K10" s="3">
         <v>53700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>52500</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -807,37 +819,41 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E12" s="3">
         <v>5400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,66 +881,75 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>800</v>
+        <v>16600</v>
       </c>
       <c r="E14" s="3">
         <v>800</v>
       </c>
       <c r="F14" s="3">
+        <v>800</v>
+      </c>
+      <c r="G14" s="3">
         <v>-700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>7600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-4100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E15" s="3">
         <v>3600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3700</v>
-      </c>
-      <c r="G15" s="3">
-        <v>3400</v>
       </c>
       <c r="H15" s="3">
         <v>3400</v>
       </c>
       <c r="I15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J15" s="3">
         <v>3300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -933,66 +958,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>122800</v>
+      </c>
+      <c r="E17" s="3">
         <v>111300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>110200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>110400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>120000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>132500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>144600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>149400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>147900</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E18" s="3">
         <v>12300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>23000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>17700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>20000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>26200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>24200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>22900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1004,71 +1036,78 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E20" s="3">
         <v>1400</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-900</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E21" s="3">
         <v>14500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>26400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>22600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>23200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>30600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>27500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>24800</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>400</v>
+        <v>2800</v>
       </c>
       <c r="E22" s="3">
         <v>400</v>
@@ -1080,77 +1119,86 @@
         <v>400</v>
       </c>
       <c r="H22" s="3">
+        <v>400</v>
+      </c>
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1000</v>
       </c>
       <c r="K22" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E23" s="3">
         <v>11200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>20400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>13500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>23800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>27300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>18700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>3100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1178,66 +1226,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E26" s="3">
         <v>8100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>18800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>27800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>14600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E27" s="3">
         <v>8100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>18800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>27800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>14600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1265,8 +1322,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1294,8 +1354,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1323,8 +1386,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1352,66 +1418,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1400</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>900</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E33" s="3">
         <v>8100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>18800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>27800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>14600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1439,71 +1514,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E35" s="3">
         <v>8100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>18800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>27800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>14600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1515,8 +1599,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1528,55 +1613,59 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>68300</v>
+      </c>
+      <c r="E41" s="3">
         <v>134300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>85000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>71300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>89400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>100200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>65100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>77800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E42" s="3">
         <v>31400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>61900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>49900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>37500</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -1586,211 +1675,235 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>116400</v>
+      </c>
+      <c r="E43" s="3">
         <v>81300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>87100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>92600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>96900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>110900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>120100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>124000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>125500</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>161400</v>
+      </c>
+      <c r="E44" s="3">
         <v>124900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>127900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>130500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>136500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>140000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>157300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>165800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>172500</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E45" s="3">
         <v>15800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>14100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>20100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>373500</v>
+      </c>
+      <c r="E46" s="3">
         <v>387600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>376000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>364300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>381500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>363000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>354300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>382600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>381400</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E47" s="3">
         <v>12500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>14000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>14600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>15500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>16400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>14600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E48" s="3">
         <v>59600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>57000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>57400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>57000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>59900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>61200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>58800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>440000</v>
+      </c>
+      <c r="E49" s="3">
         <v>72800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>72100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>73200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>76000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>76100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>77900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>78600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>79200</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1818,8 +1931,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1847,37 +1963,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E52" s="3">
         <v>32200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>31200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>30100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>29200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>30700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>30200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>29600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28600</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1905,37 +2027,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>949800</v>
+      </c>
+      <c r="E54" s="3">
         <v>584400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>567600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>555300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>571600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>559100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>552400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>574500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>560500</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1947,8 +2075,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -1960,182 +2089,201 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>49200</v>
+      </c>
+      <c r="E57" s="3">
         <v>37100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>40400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>44000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>51800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>60200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>64600</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E58" s="3">
         <v>6500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6800</v>
-      </c>
-      <c r="H58" s="3">
-        <v>6200</v>
       </c>
       <c r="I58" s="3">
         <v>6200</v>
       </c>
       <c r="J58" s="3">
+        <v>6200</v>
+      </c>
+      <c r="K58" s="3">
         <v>5200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E59" s="3">
         <v>20100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>19700</v>
       </c>
-      <c r="G59" s="3">
-        <v>18800</v>
-      </c>
       <c r="H59" s="3">
+        <v>15700</v>
+      </c>
+      <c r="I59" s="3">
         <v>23300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>27100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>34500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>128100</v>
+      </c>
+      <c r="E60" s="3">
         <v>96900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>89800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>86500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>110600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>117700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>126900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>129900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>136300</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>311300</v>
+      </c>
+      <c r="E61" s="3">
         <v>76800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>76100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>75700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>75800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>75600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>76600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>115100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>112400</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E62" s="3">
         <v>21800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>23400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>25000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23400</v>
-      </c>
-      <c r="H62" s="3">
-        <v>24500</v>
       </c>
       <c r="I62" s="3">
         <v>24500</v>
       </c>
       <c r="J62" s="3">
+        <v>24500</v>
+      </c>
+      <c r="K62" s="3">
         <v>31700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2163,8 +2311,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2192,8 +2343,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2221,37 +2375,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>508600</v>
+      </c>
+      <c r="E66" s="3">
         <v>217100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>211200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>208700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>231100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>237700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>247900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>296500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>298100</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2263,8 +2423,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2292,8 +2453,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2321,8 +2485,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2350,8 +2517,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2379,37 +2549,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>345000</v>
+      </c>
+      <c r="E72" s="3">
         <v>347700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>340500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>322500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>307500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>296400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>277800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>250900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>237200</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2437,8 +2613,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2466,8 +2645,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2495,37 +2677,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>360600</v>
+      </c>
+      <c r="E76" s="3">
         <v>367400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>356400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>346700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>340600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>321400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>304500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>278100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>262300</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2553,71 +2741,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E81" s="3">
         <v>8100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>18800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>27800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>14600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2629,8 +2826,9 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
@@ -2638,28 +2836,31 @@
         <v>3400</v>
       </c>
       <c r="E83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F83" s="3">
         <v>3300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>3300</v>
       </c>
       <c r="H83" s="3">
         <v>3300</v>
       </c>
       <c r="I83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J83" s="3">
         <v>4000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>4300</v>
       </c>
       <c r="K83" s="3">
         <v>4300</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2687,8 +2888,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2716,8 +2920,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2745,8 +2952,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2774,8 +2984,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2803,37 +3016,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E89" s="3">
         <v>27400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>32200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>26900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>40800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>23800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>16800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2845,37 +3064,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2903,8 +3126,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -2932,37 +3158,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-297300</v>
+      </c>
+      <c r="E94" s="3">
         <v>25400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-42500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>7100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -2974,13 +3206,14 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E96" s="3">
         <v>800</v>
@@ -2989,10 +3222,10 @@
         <v>800</v>
       </c>
       <c r="G96" s="3">
+        <v>800</v>
+      </c>
+      <c r="H96" s="3">
         <v>1000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>800</v>
       </c>
       <c r="I96" s="3">
         <v>800</v>
@@ -3001,10 +3234,13 @@
         <v>800</v>
       </c>
       <c r="K96" s="3">
+        <v>800</v>
+      </c>
+      <c r="L96" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3032,8 +3268,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3061,8 +3300,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3090,91 +3332,103 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>225100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-40800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-15900</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1600</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E102" s="3">
         <v>49300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-10900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>35200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BELF.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BELF.A_QTR_FIN.xlsx
@@ -653,161 +653,174 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>152200</v>
+      </c>
+      <c r="E8" s="3">
         <v>149900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>123600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>133200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>128100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>140000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>158700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>168800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>172300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>169200</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>93400</v>
+      </c>
+      <c r="E9" s="3">
         <v>93700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>79000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>79800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>80000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>88800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>103200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>113200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>118700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>116700</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>58800</v>
+      </c>
+      <c r="E10" s="3">
         <v>56200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>44700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>53400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>48100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>51200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>55500</v>
       </c>
       <c r="J10" s="3">
         <v>55500</v>
       </c>
       <c r="K10" s="3">
+        <v>55500</v>
+      </c>
+      <c r="L10" s="3">
         <v>53700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>52500</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -820,40 +833,44 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E12" s="3">
         <v>6900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -884,72 +901,81 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E14" s="3">
         <v>16600</v>
-      </c>
-      <c r="E14" s="3">
-        <v>800</v>
       </c>
       <c r="F14" s="3">
         <v>800</v>
       </c>
       <c r="G14" s="3">
+        <v>800</v>
+      </c>
+      <c r="H14" s="3">
         <v>-700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E15" s="3">
         <v>5700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>3400</v>
       </c>
       <c r="I15" s="3">
         <v>3400</v>
       </c>
       <c r="J15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K15" s="3">
         <v>3300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -959,72 +985,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>130400</v>
+      </c>
+      <c r="E17" s="3">
         <v>122800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>111300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>110200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>110400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>120000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>132500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>144600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>149400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>147900</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E18" s="3">
         <v>27100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>23000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>17700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>20000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>26200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>24200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>22900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1037,80 +1070,87 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E20" s="3">
         <v>1300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-900</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E21" s="3">
         <v>31500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>14500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>26400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>22600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>23200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>30600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>27500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>26000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>24800</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E22" s="3">
         <v>2800</v>
-      </c>
-      <c r="E22" s="3">
-        <v>400</v>
       </c>
       <c r="F22" s="3">
         <v>400</v>
@@ -1122,83 +1162,92 @@
         <v>400</v>
       </c>
       <c r="I22" s="3">
+        <v>400</v>
+      </c>
+      <c r="J22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>900</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1000</v>
       </c>
       <c r="L22" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E23" s="3">
         <v>7400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>20400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>13500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>23800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>27300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>18700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1229,72 +1278,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E26" s="3">
         <v>6400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>12000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>27800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>18800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>27800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1325,8 +1383,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1357,8 +1418,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1389,8 +1453,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1421,72 +1488,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>900</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>12000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>27800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1517,77 +1593,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>12000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>27800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1600,8 +1685,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1614,40 +1700,44 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>65900</v>
+      </c>
+      <c r="E41" s="3">
         <v>68300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>134300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>85000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>71300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>89400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>100200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>65100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>77800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1655,20 +1745,20 @@
         <v>1000</v>
       </c>
       <c r="E42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F42" s="3">
         <v>31400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>61900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>49900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>37500</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -1678,136 +1768,151 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>109200</v>
+      </c>
+      <c r="E43" s="3">
         <v>116400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>81300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>87100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>92600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>96900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>110900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>120100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>124000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>125500</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>164800</v>
+      </c>
+      <c r="E44" s="3">
         <v>161400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>124900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>127900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>130500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>136500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>140000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>157300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>165800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>172500</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E45" s="3">
         <v>26600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>14100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>20100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>368400</v>
+      </c>
+      <c r="E46" s="3">
         <v>373500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>387600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>376000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>364300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>381500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>363000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>354300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>382600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>381400</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -1815,95 +1920,104 @@
         <v>12000</v>
       </c>
       <c r="E47" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F47" s="3">
         <v>12500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>14000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>15500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>16400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>14600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>72200</v>
+      </c>
+      <c r="E48" s="3">
         <v>73000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>59600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>57000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>57400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>57000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>59900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>61200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>58800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>436400</v>
+      </c>
+      <c r="E49" s="3">
         <v>440000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>72800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>72100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>73200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>76000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>76100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>77900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>78600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>79200</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1934,8 +2048,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1966,40 +2083,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E52" s="3">
         <v>31900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>32200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>31200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>30100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>29200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>30700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28600</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2030,40 +2153,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>940500</v>
+      </c>
+      <c r="E54" s="3">
         <v>949800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>584400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>567600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>555300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>571600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>559100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>552400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>574500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>560500</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2076,8 +2205,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2090,200 +2220,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E57" s="3">
         <v>49200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>37100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>36400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>40400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>44000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>51800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>60200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>64600</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E58" s="3">
         <v>8300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6800</v>
-      </c>
-      <c r="I58" s="3">
-        <v>6200</v>
       </c>
       <c r="J58" s="3">
         <v>6200</v>
       </c>
       <c r="K58" s="3">
+        <v>6200</v>
+      </c>
+      <c r="L58" s="3">
         <v>5200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E59" s="3">
         <v>24900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>19700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>23300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>27100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>34500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>111200</v>
+      </c>
+      <c r="E60" s="3">
         <v>128100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>96900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>89800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>86500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>110600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>117700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>126900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>129900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>136300</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>302300</v>
+      </c>
+      <c r="E61" s="3">
         <v>311300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>76800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>76100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>75700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>75800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>75600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>76600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>115100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>112400</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E62" s="3">
         <v>21900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>23400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>24500</v>
       </c>
       <c r="J62" s="3">
         <v>24500</v>
       </c>
       <c r="K62" s="3">
+        <v>24500</v>
+      </c>
+      <c r="L62" s="3">
         <v>31700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2314,8 +2463,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2346,8 +2498,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2378,40 +2533,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>482500</v>
+      </c>
+      <c r="E66" s="3">
         <v>508600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>217100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>211200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>208700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>231100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>237700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>247900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>296500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>298100</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2424,8 +2585,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2456,8 +2618,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2488,8 +2653,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2520,8 +2688,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2552,40 +2723,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>362000</v>
+      </c>
+      <c r="E72" s="3">
         <v>345000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>347700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>340500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>322500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>307500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>296400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>277800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>250900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>237200</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2616,8 +2793,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2648,8 +2828,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2680,40 +2863,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>376900</v>
+      </c>
+      <c r="E76" s="3">
         <v>360600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>367400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>356400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>346700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>340600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>321400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>304500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>278100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>262300</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2744,77 +2933,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>12000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>27800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2827,40 +3025,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>3400</v>
+        <v>3700</v>
       </c>
       <c r="E83" s="3">
         <v>3400</v>
       </c>
       <c r="F83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G83" s="3">
         <v>3300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3200</v>
-      </c>
-      <c r="H83" s="3">
-        <v>3300</v>
       </c>
       <c r="I83" s="3">
         <v>3300</v>
       </c>
       <c r="J83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K83" s="3">
         <v>4000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4300</v>
       </c>
       <c r="L83" s="3">
         <v>4300</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2891,8 +3093,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2923,8 +3128,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2955,8 +3163,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2987,8 +3198,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3019,40 +3233,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E89" s="3">
         <v>8300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>27400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>32200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>26900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>40800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>23800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>16800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3065,40 +3285,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3129,8 +3353,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3161,40 +3388,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-297300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>25400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-42500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>7100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3207,16 +3440,17 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>800</v>
+      </c>
+      <c r="E96" s="3">
         <v>1000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>800</v>
       </c>
       <c r="F96" s="3">
         <v>800</v>
@@ -3225,10 +3459,10 @@
         <v>800</v>
       </c>
       <c r="H96" s="3">
+        <v>800</v>
+      </c>
+      <c r="I96" s="3">
         <v>1000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>800</v>
       </c>
       <c r="J96" s="3">
         <v>800</v>
@@ -3237,10 +3471,13 @@
         <v>800</v>
       </c>
       <c r="L96" s="3">
+        <v>800</v>
+      </c>
+      <c r="M96" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3271,8 +3508,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3303,8 +3543,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3335,100 +3578,112 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E100" s="3">
         <v>225100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-40800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-15900</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E101" s="3">
         <v>5800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1600</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-66000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>49300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-18100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>35200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BELF.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BELF.A_QTR_FIN.xlsx
@@ -653,174 +653,187 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>168300</v>
+      </c>
+      <c r="E8" s="3">
         <v>152200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>149900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>123600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>133200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>128100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>140000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>158700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>168800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>172300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>169200</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E9" s="3">
         <v>93400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>93700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>79000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>79800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>80000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>88800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>103200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>113200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>118700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>116700</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E10" s="3">
         <v>58800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>56200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>44700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>53400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>48100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>51200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>55500</v>
       </c>
       <c r="K10" s="3">
         <v>55500</v>
       </c>
       <c r="L10" s="3">
+        <v>55500</v>
+      </c>
+      <c r="M10" s="3">
         <v>53700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>52500</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -834,43 +847,47 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E12" s="3">
         <v>7200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -904,78 +921,87 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-3500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>16600</v>
-      </c>
-      <c r="F14" s="3">
-        <v>800</v>
       </c>
       <c r="G14" s="3">
         <v>800</v>
       </c>
       <c r="H14" s="3">
+        <v>800</v>
+      </c>
+      <c r="I14" s="3">
         <v>-700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-4100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E15" s="3">
         <v>6700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3700</v>
-      </c>
-      <c r="I15" s="3">
-        <v>3400</v>
       </c>
       <c r="J15" s="3">
         <v>3400</v>
       </c>
       <c r="K15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L15" s="3">
         <v>3300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -986,78 +1012,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>142400</v>
+      </c>
+      <c r="E17" s="3">
         <v>130400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>122800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>111300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>110200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>110400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>120000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>132500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>144600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>149400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>147900</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E18" s="3">
         <v>21900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>27100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>23000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>17700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>20000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>26200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>24200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>22900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1071,89 +1104,96 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-900</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E21" s="3">
         <v>30800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>31500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>14500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>26400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>22600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>23200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>30600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>27500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>24800</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E22" s="3">
         <v>4200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2800</v>
-      </c>
-      <c r="F22" s="3">
-        <v>400</v>
       </c>
       <c r="G22" s="3">
         <v>400</v>
@@ -1165,89 +1205,98 @@
         <v>400</v>
       </c>
       <c r="J22" s="3">
+        <v>400</v>
+      </c>
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>900</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1000</v>
       </c>
       <c r="M22" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E23" s="3">
         <v>23800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>22900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>20400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>27300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>18700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E24" s="3">
         <v>5500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1281,78 +1330,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E26" s="3">
         <v>18300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>18800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>12000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>27800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E27" s="3">
         <v>17900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>18800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>27800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1386,8 +1444,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1421,8 +1482,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1456,8 +1520,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1491,78 +1558,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E32" s="3">
         <v>2200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>900</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E33" s="3">
         <v>17900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>27800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1596,83 +1672,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E35" s="3">
         <v>17900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>27800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1686,8 +1771,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1701,67 +1787,71 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E41" s="3">
         <v>65900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>68300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>134300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>85000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>71300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>89400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>100200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>65100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>77800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>1000</v>
       </c>
       <c r="F42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G42" s="3">
         <v>31400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>61900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>49900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>37500</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -1771,148 +1861,163 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>127600</v>
+      </c>
+      <c r="E43" s="3">
         <v>109200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>116400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>81300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>87100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>92600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>96900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>110900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>120100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>124000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>125500</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>164600</v>
+      </c>
+      <c r="E44" s="3">
         <v>164800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>161400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>124900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>127900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>130500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>136500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>140000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>157300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>165800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>172500</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E45" s="3">
         <v>27500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>26600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>14100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>378600</v>
+      </c>
+      <c r="E46" s="3">
         <v>368400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>373500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>387600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>376000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>364300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>381500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>363000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>354300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>382600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>381400</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -1923,101 +2028,110 @@
         <v>12000</v>
       </c>
       <c r="F47" s="3">
+        <v>12000</v>
+      </c>
+      <c r="G47" s="3">
         <v>12500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>15500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>16400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>14600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>72600</v>
+      </c>
+      <c r="E48" s="3">
         <v>72200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>73000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>59600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>57000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>57400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>57000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>59900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>61200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>58800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>436300</v>
+      </c>
+      <c r="E49" s="3">
         <v>436400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>440000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>72800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>72100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>73200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>76000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>76100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>77900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>78600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>79200</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2051,8 +2165,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2086,43 +2203,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E52" s="3">
         <v>31100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>31900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>32200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>31200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>30100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>29200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>28600</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2156,43 +2279,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>950600</v>
+      </c>
+      <c r="E54" s="3">
         <v>940500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>949800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>584400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>567600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>555300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>571600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>559100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>552400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>574500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>560500</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2206,8 +2335,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2221,218 +2351,237 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E57" s="3">
         <v>46100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>49200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>37100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>36400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>40400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>44000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>51800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>60200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>64600</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E58" s="3">
         <v>8500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6800</v>
-      </c>
-      <c r="J58" s="3">
-        <v>6200</v>
       </c>
       <c r="K58" s="3">
         <v>6200</v>
       </c>
       <c r="L58" s="3">
+        <v>6200</v>
+      </c>
+      <c r="M58" s="3">
         <v>5200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E59" s="3">
         <v>21500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>24900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>23300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>27100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>34500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>124100</v>
+      </c>
+      <c r="E60" s="3">
         <v>111200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>128100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>96900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>89800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>86500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>110600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>117700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>126900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>129900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>136300</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>269700</v>
+      </c>
+      <c r="E61" s="3">
         <v>302300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>311300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>76800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>76100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>75700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>75800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>75600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>76600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>115100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>112400</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E62" s="3">
         <v>23400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>21800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>23400</v>
-      </c>
-      <c r="J62" s="3">
-        <v>24500</v>
       </c>
       <c r="K62" s="3">
         <v>24500</v>
       </c>
       <c r="L62" s="3">
+        <v>24500</v>
+      </c>
+      <c r="M62" s="3">
         <v>31700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2466,8 +2615,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2501,8 +2653,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2536,43 +2691,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>464900</v>
+      </c>
+      <c r="E66" s="3">
         <v>482500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>508600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>217100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>211200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>208700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>231100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>237700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>247900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>296500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>298100</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2586,8 +2747,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2621,8 +2783,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2656,8 +2821,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2691,8 +2859,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2726,43 +2897,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>388000</v>
+      </c>
+      <c r="E72" s="3">
         <v>362000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>345000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>347700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>340500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>322500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>307500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>296400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>277800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>250900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>237200</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2796,8 +2973,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2831,8 +3011,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2866,43 +3049,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>404700</v>
+      </c>
+      <c r="E76" s="3">
         <v>376900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>360600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>367400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>356400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>346700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>340600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>321400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>304500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>278100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>262300</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2936,83 +3125,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E81" s="3">
         <v>17900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>27800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3026,43 +3224,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E83" s="3">
         <v>3700</v>
-      </c>
-      <c r="E83" s="3">
-        <v>3400</v>
       </c>
       <c r="F83" s="3">
         <v>3400</v>
       </c>
       <c r="G83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H83" s="3">
         <v>3300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>3300</v>
       </c>
       <c r="J83" s="3">
         <v>3300</v>
       </c>
       <c r="K83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L83" s="3">
         <v>4000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>4300</v>
       </c>
       <c r="M83" s="3">
         <v>4300</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3096,8 +3298,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3131,8 +3336,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3166,8 +3374,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3201,8 +3412,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3236,43 +3450,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E89" s="3">
         <v>8100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>27400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>32200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>26900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>40800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>23800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>16800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3286,43 +3506,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3356,8 +3580,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3391,43 +3618,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-297300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>25400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-42500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>7100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3441,8 +3674,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -3450,10 +3684,10 @@
         <v>800</v>
       </c>
       <c r="E96" s="3">
+        <v>800</v>
+      </c>
+      <c r="F96" s="3">
         <v>1000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>800</v>
       </c>
       <c r="G96" s="3">
         <v>800</v>
@@ -3462,10 +3696,10 @@
         <v>800</v>
       </c>
       <c r="I96" s="3">
+        <v>800</v>
+      </c>
+      <c r="J96" s="3">
         <v>1000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>800</v>
       </c>
       <c r="K96" s="3">
         <v>800</v>
@@ -3474,10 +3708,13 @@
         <v>800</v>
       </c>
       <c r="M96" s="3">
+        <v>800</v>
+      </c>
+      <c r="N96" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3511,8 +3748,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3546,8 +3786,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3581,109 +3824,121 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-31500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>225100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-40800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-15900</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1600</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-66000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>49300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>35200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BELF.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BELF.A_QTR_FIN.xlsx
@@ -653,200 +653,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>175900</v>
+      </c>
+      <c r="E8" s="3">
         <v>179000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>168300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>152200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>149900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>123600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>133200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>128100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>140000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>158700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>168800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>172300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>169200</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>106600</v>
+      </c>
+      <c r="E9" s="3">
         <v>107800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>103200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>93400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>93700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>79000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>79800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>80000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>88800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>103200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>113200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>118700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>116700</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E10" s="3">
         <v>71100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>65100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>58800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>56200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>44700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>53400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>48100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>51200</v>
-      </c>
-      <c r="L10" s="3">
-        <v>55500</v>
       </c>
       <c r="M10" s="3">
         <v>55500</v>
       </c>
       <c r="N10" s="3">
+        <v>55500</v>
+      </c>
+      <c r="O10" s="3">
         <v>53700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>52500</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,49 +874,53 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E12" s="3">
         <v>7500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,49 +960,55 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-3700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>16600</v>
-      </c>
-      <c r="H14" s="3">
-        <v>800</v>
       </c>
       <c r="I14" s="3">
         <v>800</v>
       </c>
       <c r="J14" s="3">
+        <v>800</v>
+      </c>
+      <c r="K14" s="3">
         <v>-700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-4100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -994,40 +1016,43 @@
         <v>6700</v>
       </c>
       <c r="E15" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F15" s="3">
         <v>6600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3700</v>
-      </c>
-      <c r="K15" s="3">
-        <v>3400</v>
       </c>
       <c r="L15" s="3">
         <v>3400</v>
       </c>
       <c r="M15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="N15" s="3">
         <v>3300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1040,90 +1065,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>147400</v>
+      </c>
+      <c r="E17" s="3">
         <v>148400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>142400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>130400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>122800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>111300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>110200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>110400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>120000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>132500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>144600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>149400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>147900</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E18" s="3">
         <v>30600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>25900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>21900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>27100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>23000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>26200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>22900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1139,107 +1171,114 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1400</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-900</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E21" s="3">
         <v>38100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>40300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>30800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>31500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>14500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>26400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>22600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>23200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>30600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>27500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>26000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>24800</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E22" s="3">
         <v>3600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2800</v>
-      </c>
-      <c r="H22" s="3">
-        <v>400</v>
       </c>
       <c r="I22" s="3">
         <v>400</v>
@@ -1251,101 +1290,110 @@
         <v>400</v>
       </c>
       <c r="L22" s="3">
+        <v>400</v>
+      </c>
+      <c r="M22" s="3">
         <v>500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>900</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1000</v>
       </c>
       <c r="O22" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E23" s="3">
         <v>28000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>33700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>23800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>22900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>20400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>27300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>18700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E24" s="3">
         <v>5400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1385,90 +1433,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E26" s="3">
         <v>22600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>26800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>12000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>27800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E27" s="3">
         <v>22300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>26900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>12000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>27800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1508,8 +1565,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1549,8 +1609,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1590,8 +1653,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1631,90 +1697,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E32" s="3">
         <v>900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1400</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>900</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E33" s="3">
         <v>22300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>26900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>27800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1754,95 +1829,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E35" s="3">
         <v>22300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>26900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>27800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1858,8 +1942,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1875,49 +1960,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E41" s="3">
         <v>57700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>59300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>65900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>68300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>134300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>85000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>71300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>89400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>65100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>77800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1928,26 +2017,26 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>1000</v>
       </c>
       <c r="H42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I42" s="3">
         <v>31400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>61900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>49900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>37500</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -1957,180 +2046,195 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>131200</v>
+      </c>
+      <c r="E43" s="3">
         <v>135100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>127600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>109200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>116400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>81300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>87100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>92600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>96900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>110900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>120100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>124000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>125500</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>167300</v>
+      </c>
+      <c r="E44" s="3">
         <v>166100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>164600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>164800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>161400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>124900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>127900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>130500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>136500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>140000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>157300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>165800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>172500</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E45" s="3">
         <v>28700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>27000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>27500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>26600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>20100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>384800</v>
+      </c>
+      <c r="E46" s="3">
         <v>387700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>378600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>368400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>373500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>387600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>376000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>364300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>381500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>363000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>354300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>382600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>381400</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>900</v>
+      </c>
+      <c r="E47" s="3">
         <v>11300</v>
-      </c>
-      <c r="E47" s="3">
-        <v>12000</v>
       </c>
       <c r="F47" s="3">
         <v>12000</v>
@@ -2139,113 +2243,122 @@
         <v>12000</v>
       </c>
       <c r="H47" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I47" s="3">
         <v>12500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>14600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>14200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>15500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>16400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>14600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>71300</v>
+      </c>
+      <c r="E48" s="3">
         <v>69500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>72600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>72200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>73000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>59600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>57000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>57400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>57000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>59900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>61200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>58800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>432800</v>
+      </c>
+      <c r="E49" s="3">
         <v>435900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>436300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>436400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>440000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>72800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>72100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>73200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>76000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>76100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>77900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>78600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>79200</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2285,8 +2398,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2326,49 +2442,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E52" s="3">
         <v>31800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>31400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>31100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>31900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>32200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>30700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>29600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>28600</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2408,49 +2530,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>935200</v>
+      </c>
+      <c r="E54" s="3">
         <v>952800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>950600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>940500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>949800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>584400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>567600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>555300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>571600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>559100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>552400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>574500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>560500</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2466,8 +2594,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2483,254 +2612,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E57" s="3">
         <v>54200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>53700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>46100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>49200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>37100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>36400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>32800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>40400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>44000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>51800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>60200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>64600</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E58" s="3">
         <v>8200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6800</v>
-      </c>
-      <c r="L58" s="3">
-        <v>6200</v>
       </c>
       <c r="M58" s="3">
         <v>6200</v>
       </c>
       <c r="N58" s="3">
+        <v>6200</v>
+      </c>
+      <c r="O58" s="3">
         <v>5200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E59" s="3">
         <v>20300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>23100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>24900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>23300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>34500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>127400</v>
+      </c>
+      <c r="E60" s="3">
         <v>126800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>124100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>111200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>128100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>96900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>89800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>86500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>110600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>117700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>126900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>129900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>136300</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>214200</v>
+      </c>
+      <c r="E61" s="3">
         <v>241200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>269700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>302300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>311300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>76800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>76100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>75700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>75800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>75600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>76600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>115100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>112400</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E62" s="3">
         <v>26800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>21900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>21800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>23400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>25000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23400</v>
-      </c>
-      <c r="L62" s="3">
-        <v>24500</v>
       </c>
       <c r="M62" s="3">
         <v>24500</v>
       </c>
       <c r="N62" s="3">
+        <v>24500</v>
+      </c>
+      <c r="O62" s="3">
         <v>31700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2770,8 +2918,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2811,8 +2962,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2852,49 +3006,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>416500</v>
+      </c>
+      <c r="E66" s="3">
         <v>443800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>464900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>482500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>508600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>217100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>211200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>208700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>231100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>237700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>247900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>296500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>298100</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2910,8 +3070,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2951,8 +3112,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2992,8 +3156,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3033,8 +3200,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3074,49 +3244,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>403100</v>
+      </c>
+      <c r="E72" s="3">
         <v>409400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>388000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>362000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>345000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>347700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>340500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>322500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>307500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>296400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>277800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>250900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>237200</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3156,8 +3332,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3197,8 +3376,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3238,49 +3420,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>425500</v>
+      </c>
+      <c r="E76" s="3">
         <v>427800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>404700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>376900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>360600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>367400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>356400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>346700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>340600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>321400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>304500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>278100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>262300</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3320,95 +3508,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E81" s="3">
         <v>22300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>26900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>27800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3424,49 +3621,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E83" s="3">
         <v>3600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3700</v>
-      </c>
-      <c r="G83" s="3">
-        <v>3400</v>
       </c>
       <c r="H83" s="3">
         <v>3400</v>
       </c>
       <c r="I83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J83" s="3">
         <v>3300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3200</v>
-      </c>
-      <c r="K83" s="3">
-        <v>3300</v>
       </c>
       <c r="L83" s="3">
         <v>3300</v>
       </c>
       <c r="M83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N83" s="3">
         <v>4000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>4300</v>
       </c>
       <c r="O83" s="3">
         <v>4300</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3506,8 +3707,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3547,8 +3751,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3588,8 +3795,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3629,8 +3839,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3670,49 +3883,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E89" s="3">
         <v>22200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>20700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>27400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>32200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>26900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>40800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>23800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>16800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3728,49 +3947,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3810,8 +4033,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3851,49 +4077,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E94" s="3">
         <v>800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-297300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>25400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-42500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>7100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3909,13 +4141,14 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E96" s="3">
         <v>800</v>
@@ -3924,10 +4157,10 @@
         <v>800</v>
       </c>
       <c r="G96" s="3">
+        <v>800</v>
+      </c>
+      <c r="H96" s="3">
         <v>1000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>800</v>
       </c>
       <c r="I96" s="3">
         <v>800</v>
@@ -3936,10 +4169,10 @@
         <v>800</v>
       </c>
       <c r="K96" s="3">
+        <v>800</v>
+      </c>
+      <c r="L96" s="3">
         <v>1000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>800</v>
       </c>
       <c r="M96" s="3">
         <v>800</v>
@@ -3948,10 +4181,13 @@
         <v>800</v>
       </c>
       <c r="O96" s="3">
+        <v>800</v>
+      </c>
+      <c r="P96" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3991,8 +4227,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4032,8 +4271,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4073,127 +4315,139 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-25800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-31500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>225100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-40800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-15900</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>5800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1600</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-66000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>49300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>35200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-600</v>
       </c>
     </row>
